--- a/docs/configs/Turrets.xlsx
+++ b/docs/configs/Turrets.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgTurret" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#Projectile" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#TurretSlots" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +29,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -43,8 +41,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,11 +63,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,26 +433,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>炮塔ID</t>
+          <t>编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -465,408 +461,1035 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>射程(px)</t>
+          <t>图标Key</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>射程</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>伤害</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>冷却(秒)</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>弹道类型</t>
+          <t>冷却</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>弹速(px/s)</t>
+          <t>颜色R</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>弹道生命(秒)</t>
+          <t>颜色G</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>AOE半径(px)</t>
+          <t>颜色B</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>AOE衰减</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>锥形半角(弧度)</t>
+          <t>投射物类型</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>string:client</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>ImgKey</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>ColorR</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>ColorG</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>ColorB</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>ProjType</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>弓箭炮塔</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>arrow</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>220</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>180</v>
+      </c>
+      <c r="H4" t="n">
+        <v>140</v>
+      </c>
+      <c r="I4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>狙击炮塔</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sniper</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>350</v>
+      </c>
+      <c r="E5" t="n">
+        <v>35</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>255</v>
+      </c>
+      <c r="H5" t="n">
+        <v>60</v>
+      </c>
+      <c r="I5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sniper</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>喷火炮塔</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>flame</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>255</v>
+      </c>
+      <c r="H6" t="n">
+        <v>120</v>
+      </c>
+      <c r="I6" t="n">
+        <v>30</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>flame</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>电能炮塔</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="n">
+        <v>160</v>
+      </c>
+      <c r="I7" t="n">
+        <v>255</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>electric</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>火箭炮塔</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>280</v>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>80</v>
+      </c>
+      <c r="H8" t="n">
+        <v>120</v>
+      </c>
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>机关枪炮塔</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>minigun</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>250</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>255</v>
+      </c>
+      <c r="H9" t="n">
+        <v>230</v>
+      </c>
+      <c r="I9" t="n">
+        <v>80</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>minigun</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ARROW_SPEED</t>
+        </is>
+      </c>
+      <c r="C1" t="n">
+        <v>280</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>弓箭飞行速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ARROW_LIFE</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>弓箭最大存活时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ARROW_HIT_RADIUS_SQ</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>弓箭命中判定距离²</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MINIGUN_SPEED</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>机关枪弹速</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MINIGUN_LIFE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>机关枪弹存活时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MINIGUN_SPREAD</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>机关枪散布角度</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MINIGUN_HIT_RADIUS_SQ</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>144</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>机关枪命中距离²</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ROCKET_SPEED</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>150</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>火箭飞行速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ROCKET_LIFE</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>火箭最大存活时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ROCKET_AOE_RADIUS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>80</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>火箭爆炸半径(像素)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ROCKET_AOE_FALLOFF</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>火箭AOE边缘衰减比</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ROCKET_HIT_RADIUS_SQ</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>225</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>火箭命中判定距离²</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ROCKET_TRAIL_INTERVAL</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>火箭烟尾生成间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SNIPER_SEGMENTS_PER10</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>狙击射线每10px段数</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SNIPER_LIFE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>狙击射线存活时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SNIPER_SPARK_COUNT</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>狙击命中火花数</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ELECTRIC_LIFE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>闪电弧存活时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ELECTRIC_OFFSET</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>闪电弧偏移量</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ELECTRIC_SPARK_COUNT</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>闪电命中火花数</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>FLAME_HALF_SPREAD</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>火焰半扩散角(弧度)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FLAME_DRAW_H</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>130</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>火焰视觉长度</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TURRET_H</t>
+        </is>
+      </c>
+      <c r="C1" t="n">
+        <v>48</v>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>炮塔渲染高度</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TURRET_W</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>36</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>炮塔渲染宽度</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Cooldown</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ProjType</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>ProjSpeed</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>ProjLife</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>AoeRadius</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>AoeFalloff</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>ConeHalfAngle</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SLOT1_OFFSET_X</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>-18</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>左侧槽位X偏移</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>arrow</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>弓箭炮塔</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>220</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>arrow</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I4" s="2" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SLOT1_OFFSET_Y</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>左侧槽位Y偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SLOT2_OFFSET_X</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>右侧槽位X偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SLOT2_OFFSET_Y</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>右侧槽位Y偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SLOT3_OFFSET_X</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>车头槽位X偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SLOT3_OFFSET_Y</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>36</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>车头槽位Y偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SLOT4_OFFSET_X</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>sniper</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>狙击炮塔</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>350</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>sniper</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>flame</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>喷火炮塔</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>flame</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>电能炮塔</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>electric</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>rocket</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>火箭炮塔</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>280</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>rocket</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>minigun</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>机关枪塔</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>minigun</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>车尾槽位X偏移</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SLOT4_OFFSET_Y</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-32</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>车尾槽位Y偏移</t>
+        </is>
       </c>
     </row>
   </sheetData>
